--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,97 +421,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ngay_cong_bo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>linh_vuc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>loai_hinh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>trang_thai_xep_hang</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>loai_y_kien</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ky_han</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ket_qua_xep_hang</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>trien_vong</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ma_trai_phieu</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bao_cao_vi</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>bao_cao_en</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>link_to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>issuer_id</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>bao_mat</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>phi_tren_5pc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>to_chuc_xhtn</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>thoi_gian_scrape</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ngay_cong_bo_dt</t>
         </is>
@@ -589,10 +577,10 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>46281</v>
       </c>
     </row>
@@ -656,10 +644,10 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>46280</v>
       </c>
     </row>
@@ -715,10 +703,10 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="n">
         <v>46280</v>
       </c>
     </row>
@@ -774,10 +762,10 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>46277</v>
       </c>
     </row>
@@ -837,10 +825,10 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>46275</v>
       </c>
     </row>
@@ -908,10 +896,10 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="n">
         <v>46273</v>
       </c>
     </row>
@@ -979,10 +967,10 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>46268</v>
       </c>
     </row>
@@ -1050,10 +1038,10 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>46262</v>
       </c>
     </row>
@@ -1121,10 +1109,10 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>46261</v>
       </c>
     </row>
@@ -1192,10 +1180,10 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="n">
         <v>46261</v>
       </c>
     </row>
@@ -1263,10 +1251,10 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="n">
         <v>46261</v>
       </c>
     </row>
@@ -1334,10 +1322,10 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>46260</v>
       </c>
     </row>
@@ -1401,10 +1389,10 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>46260</v>
       </c>
     </row>
@@ -1472,10 +1460,10 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>46259</v>
       </c>
     </row>
@@ -1543,10 +1531,10 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="n">
         <v>46258</v>
       </c>
     </row>
@@ -1610,10 +1598,10 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="n">
         <v>46255</v>
       </c>
     </row>
@@ -1677,10 +1665,10 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>46253</v>
       </c>
     </row>
@@ -1744,10 +1732,10 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S19" s="1" t="n">
         <v>46252</v>
       </c>
     </row>
@@ -1811,10 +1799,10 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="n">
         <v>46249</v>
       </c>
     </row>
@@ -1878,10 +1866,10 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="n">
         <v>46247</v>
       </c>
     </row>
@@ -1945,10 +1933,10 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S22" s="1" t="n">
         <v>46247</v>
       </c>
     </row>
@@ -2012,10 +2000,10 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S23" s="1" t="n">
         <v>46243</v>
       </c>
     </row>
@@ -2079,10 +2067,10 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="n">
         <v>46237</v>
       </c>
     </row>
@@ -2146,10 +2134,10 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S25" s="1" t="n">
         <v>46231</v>
       </c>
     </row>
@@ -2213,10 +2201,10 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="n">
         <v>46231</v>
       </c>
     </row>
@@ -2280,10 +2268,10 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S27" s="1" t="n">
         <v>46225</v>
       </c>
     </row>
@@ -2351,10 +2339,10 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -2418,10 +2406,10 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S29" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -2489,10 +2477,10 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S30" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -2556,10 +2544,10 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S31" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -2627,10 +2615,10 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S32" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -2698,10 +2686,10 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -2765,10 +2753,10 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -2836,10 +2824,10 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -2907,10 +2895,10 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -2970,10 +2958,10 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -3037,10 +3025,10 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -3104,10 +3092,10 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S39" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -3175,10 +3163,10 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -3242,10 +3230,10 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -3309,10 +3297,10 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -3380,10 +3368,10 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S43" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -3451,10 +3439,10 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S44" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -3518,10 +3506,10 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S45" s="1" t="n">
         <v>46200</v>
       </c>
     </row>
@@ -3589,10 +3577,10 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S46" s="1" t="n">
         <v>46199</v>
       </c>
     </row>
@@ -3660,10 +3648,10 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S47" s="1" t="n">
         <v>46199</v>
       </c>
     </row>
@@ -3731,10 +3719,10 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S48" s="1" t="n">
         <v>46199</v>
       </c>
     </row>
@@ -3798,10 +3786,10 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S49" s="1" t="n">
         <v>46198</v>
       </c>
     </row>
@@ -3865,10 +3853,10 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S50" s="1" t="n">
         <v>46198</v>
       </c>
     </row>
@@ -3932,10 +3920,10 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S51" s="1" t="n">
         <v>46196</v>
       </c>
     </row>
@@ -4003,10 +3991,10 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S52" s="1" t="n">
         <v>46195</v>
       </c>
     </row>
@@ -4074,10 +4062,10 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S53" s="1" t="n">
         <v>46192</v>
       </c>
     </row>
@@ -4145,10 +4133,10 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S54" s="1" t="n">
         <v>46192</v>
       </c>
     </row>
@@ -4212,10 +4200,10 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S55" s="1" t="n">
         <v>46191</v>
       </c>
     </row>
@@ -4283,10 +4271,10 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S56" s="1" t="n">
         <v>46190</v>
       </c>
     </row>
@@ -4354,10 +4342,10 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S57" s="1" t="n">
         <v>46190</v>
       </c>
     </row>
@@ -4425,10 +4413,10 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S58" s="1" t="n">
         <v>46190</v>
       </c>
     </row>
@@ -4496,10 +4484,10 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S59" s="1" t="n">
         <v>46190</v>
       </c>
     </row>
@@ -4563,10 +4551,10 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S60" s="1" t="n">
         <v>46189</v>
       </c>
     </row>
@@ -4630,10 +4618,10 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S61" s="1" t="n">
         <v>46185</v>
       </c>
     </row>
@@ -4697,10 +4685,10 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S62" s="1" t="n">
         <v>46185</v>
       </c>
     </row>
@@ -4764,10 +4752,10 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S63" s="1" t="n">
         <v>46185</v>
       </c>
     </row>
@@ -4831,10 +4819,10 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S64" s="1" t="n">
         <v>46182</v>
       </c>
     </row>
@@ -4898,10 +4886,10 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S65" s="1" t="n">
         <v>46181</v>
       </c>
     </row>
@@ -4965,10 +4953,10 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S66" s="1" t="n">
         <v>46181</v>
       </c>
     </row>
@@ -5032,10 +5020,10 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S67" s="1" t="n">
         <v>46177</v>
       </c>
     </row>
@@ -5099,10 +5087,10 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S68" s="1" t="n">
         <v>46177</v>
       </c>
     </row>
@@ -5170,10 +5158,10 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S69" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -5241,10 +5229,10 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S70" s="1" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -5308,10 +5296,10 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S71" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S71" s="1" t="n">
         <v>46172</v>
       </c>
     </row>
@@ -5379,10 +5367,10 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S72" s="1" t="n">
         <v>46169</v>
       </c>
     </row>
@@ -5450,10 +5438,10 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S73" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S73" s="1" t="n">
         <v>46169</v>
       </c>
     </row>
@@ -5517,10 +5505,10 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S74" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S74" s="1" t="n">
         <v>46168</v>
       </c>
     </row>
@@ -5588,10 +5576,10 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S75" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S75" s="1" t="n">
         <v>46167</v>
       </c>
     </row>
@@ -5659,10 +5647,10 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S76" s="1" t="n">
         <v>46167</v>
       </c>
     </row>
@@ -5726,10 +5714,10 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S77" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S77" s="1" t="n">
         <v>46167</v>
       </c>
     </row>
@@ -5793,10 +5781,10 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S78" s="1" t="n">
         <v>46167</v>
       </c>
     </row>
@@ -5860,10 +5848,10 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S79" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S79" s="1" t="n">
         <v>46163</v>
       </c>
     </row>
@@ -5927,10 +5915,10 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S80" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S80" s="1" t="n">
         <v>46163</v>
       </c>
     </row>
@@ -5998,10 +5986,10 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S81" s="1" t="n">
         <v>46161</v>
       </c>
     </row>
@@ -6065,10 +6053,10 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="n">
         <v>46160</v>
       </c>
     </row>
@@ -6136,10 +6124,10 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S83" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S83" s="1" t="n">
         <v>46154</v>
       </c>
     </row>
@@ -6203,10 +6191,10 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S84" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S84" s="1" t="n">
         <v>46153</v>
       </c>
     </row>
@@ -6270,10 +6258,10 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S85" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S85" s="1" t="n">
         <v>46153</v>
       </c>
     </row>
@@ -6337,10 +6325,10 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S86" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S86" s="1" t="n">
         <v>46149</v>
       </c>
     </row>
@@ -6408,10 +6396,10 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S87" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S87" s="1" t="n">
         <v>46148</v>
       </c>
     </row>
@@ -6479,10 +6467,10 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S88" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S88" s="1" t="n">
         <v>46148</v>
       </c>
     </row>
@@ -6550,10 +6538,10 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S89" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S89" s="1" t="n">
         <v>46148</v>
       </c>
     </row>
@@ -6617,10 +6605,10 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S90" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S90" s="1" t="n">
         <v>46148</v>
       </c>
     </row>
@@ -6684,10 +6672,10 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S91" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S91" s="1" t="n">
         <v>46146</v>
       </c>
     </row>
@@ -6755,10 +6743,10 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S92" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S92" s="1" t="n">
         <v>46146</v>
       </c>
     </row>
@@ -6822,10 +6810,10 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S93" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S93" s="1" t="n">
         <v>46136</v>
       </c>
     </row>
@@ -6893,10 +6881,10 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S94" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S94" s="1" t="n">
         <v>46133</v>
       </c>
     </row>
@@ -6964,10 +6952,10 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S95" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S95" s="1" t="n">
         <v>46133</v>
       </c>
     </row>
@@ -7035,10 +7023,10 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S96" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S96" s="1" t="n">
         <v>46133</v>
       </c>
     </row>
@@ -7102,10 +7090,10 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S97" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S97" s="1" t="n">
         <v>46132</v>
       </c>
     </row>
@@ -7169,10 +7157,10 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S98" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S98" s="1" t="n">
         <v>46132</v>
       </c>
     </row>
@@ -7236,10 +7224,10 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S99" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S99" s="1" t="n">
         <v>46132</v>
       </c>
     </row>
@@ -7303,10 +7291,10 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S100" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S100" s="1" t="n">
         <v>46126</v>
       </c>
     </row>
@@ -7370,10 +7358,10 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S101" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S101" s="1" t="n">
         <v>46126</v>
       </c>
     </row>
@@ -7437,10 +7425,10 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S102" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S102" s="1" t="n">
         <v>46122</v>
       </c>
     </row>
@@ -7504,10 +7492,10 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S103" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S103" s="1" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -7571,10 +7559,10 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S104" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S104" s="1" t="n">
         <v>46114</v>
       </c>
     </row>
@@ -7638,10 +7626,10 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S105" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S105" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -7705,10 +7693,10 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S106" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S106" s="1" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -7772,10 +7760,10 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S107" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S107" s="1" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -7839,10 +7827,10 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S108" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S108" s="1" t="n">
         <v>46111</v>
       </c>
     </row>
@@ -7910,10 +7898,10 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S109" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S109" s="1" t="n">
         <v>46111</v>
       </c>
     </row>
@@ -7977,10 +7965,10 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S110" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S110" s="1" t="n">
         <v>46107</v>
       </c>
     </row>
@@ -8044,10 +8032,10 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S111" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S111" s="1" t="n">
         <v>46106</v>
       </c>
     </row>
@@ -8111,10 +8099,10 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S112" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S112" s="1" t="n">
         <v>46099</v>
       </c>
     </row>
@@ -8178,10 +8166,10 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S113" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S113" s="1" t="n">
         <v>46099</v>
       </c>
     </row>
@@ -8245,10 +8233,10 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S114" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S114" s="1" t="n">
         <v>46098</v>
       </c>
     </row>
@@ -8312,10 +8300,10 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S115" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S115" s="1" t="n">
         <v>46097</v>
       </c>
     </row>
@@ -8379,10 +8367,10 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S116" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S116" s="1" t="n">
         <v>46094</v>
       </c>
     </row>
@@ -8442,10 +8430,10 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S117" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S117" s="1" t="n">
         <v>46091</v>
       </c>
     </row>
@@ -8509,10 +8497,10 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S118" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S118" s="1" t="n">
         <v>46078</v>
       </c>
     </row>
@@ -8576,10 +8564,10 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S119" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S119" s="1" t="n">
         <v>46078</v>
       </c>
     </row>
@@ -8643,10 +8631,10 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S120" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S120" s="1" t="n">
         <v>46068</v>
       </c>
     </row>
@@ -8710,10 +8698,10 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S121" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S121" s="1" t="n">
         <v>46065</v>
       </c>
     </row>
@@ -8777,10 +8765,10 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S122" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S122" s="1" t="n">
         <v>46064</v>
       </c>
     </row>
@@ -8844,10 +8832,10 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S123" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S123" s="1" t="n">
         <v>46063</v>
       </c>
     </row>
@@ -8911,10 +8899,10 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S124" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S124" s="1" t="n">
         <v>46062</v>
       </c>
     </row>
@@ -8978,10 +8966,10 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S125" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S125" s="1" t="n">
         <v>46057</v>
       </c>
     </row>
@@ -9045,10 +9033,10 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S126" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S126" s="1" t="n">
         <v>46053</v>
       </c>
     </row>
@@ -9112,10 +9100,10 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S127" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S127" s="1" t="n">
         <v>46044</v>
       </c>
     </row>
@@ -9179,10 +9167,10 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S128" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S128" s="1" t="n">
         <v>46036</v>
       </c>
     </row>
@@ -9246,10 +9234,10 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S129" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S129" s="1" t="n">
         <v>46032</v>
       </c>
     </row>
@@ -9313,10 +9301,10 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S130" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S130" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -9384,10 +9372,10 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S131" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S131" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -9455,10 +9443,10 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S132" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S132" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -9522,10 +9510,10 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S133" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S133" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -9589,10 +9577,10 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S134" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S134" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -9660,10 +9648,10 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S135" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S135" s="1" t="n">
         <v>46016</v>
       </c>
     </row>
@@ -9727,10 +9715,10 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S136" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S136" s="1" t="n">
         <v>46009</v>
       </c>
     </row>
@@ -9794,10 +9782,10 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S137" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S137" s="1" t="n">
         <v>46008</v>
       </c>
     </row>
@@ -9861,10 +9849,10 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S138" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S138" s="1" t="n">
         <v>46007</v>
       </c>
     </row>
@@ -9928,10 +9916,10 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S139" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S139" s="1" t="n">
         <v>46003</v>
       </c>
     </row>
@@ -9995,10 +9983,10 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S140" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S140" s="1" t="n">
         <v>45999</v>
       </c>
     </row>
@@ -10062,10 +10050,10 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S141" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S141" s="1" t="n">
         <v>45999</v>
       </c>
     </row>
@@ -10129,10 +10117,10 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S142" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S142" s="1" t="n">
         <v>45995</v>
       </c>
     </row>
@@ -10196,10 +10184,10 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S143" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S143" s="1" t="n">
         <v>45987</v>
       </c>
     </row>
@@ -10263,10 +10251,10 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S144" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S144" s="1" t="n">
         <v>45986</v>
       </c>
     </row>
@@ -10330,10 +10318,10 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S145" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S145" s="1" t="n">
         <v>45986</v>
       </c>
     </row>
@@ -10397,10 +10385,10 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S146" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S146" s="1" t="n">
         <v>45982</v>
       </c>
     </row>
@@ -10464,10 +10452,10 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S147" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S147" s="1" t="n">
         <v>45981</v>
       </c>
     </row>
@@ -10531,10 +10519,10 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S148" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S148" s="1" t="n">
         <v>45979</v>
       </c>
     </row>
@@ -10598,10 +10586,10 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S149" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S149" s="1" t="n">
         <v>45975</v>
       </c>
     </row>
@@ -10665,10 +10653,10 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S150" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S150" s="1" t="n">
         <v>45964</v>
       </c>
     </row>
@@ -10732,10 +10720,10 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S151" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S151" s="1" t="n">
         <v>45960</v>
       </c>
     </row>
@@ -10799,10 +10787,10 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S152" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S152" s="1" t="n">
         <v>45950</v>
       </c>
     </row>
@@ -10866,10 +10854,10 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S153" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S153" s="1" t="n">
         <v>45946</v>
       </c>
     </row>
@@ -10933,10 +10921,10 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S154" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S154" s="1" t="n">
         <v>45940</v>
       </c>
     </row>
@@ -11000,10 +10988,10 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S155" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S155" s="1" t="n">
         <v>45938</v>
       </c>
     </row>
@@ -11067,10 +11055,10 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S156" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S156" s="1" t="n">
         <v>45933</v>
       </c>
     </row>
@@ -11134,10 +11122,10 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S157" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S157" s="1" t="n">
         <v>45933</v>
       </c>
     </row>
@@ -11201,10 +11189,10 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S158" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S158" s="1" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -11268,10 +11256,10 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S159" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S159" s="1" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -11335,10 +11323,10 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S160" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S160" s="1" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -11402,10 +11390,10 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S161" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S161" s="1" t="n">
         <v>45926</v>
       </c>
     </row>
@@ -11469,10 +11457,10 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S162" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S162" s="1" t="n">
         <v>45922</v>
       </c>
     </row>
@@ -11536,10 +11524,10 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S163" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S163" s="1" t="n">
         <v>45919</v>
       </c>
     </row>
@@ -11603,10 +11591,10 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S164" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S164" s="1" t="n">
         <v>45919</v>
       </c>
     </row>
@@ -11670,10 +11658,10 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S165" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S165" s="1" t="n">
         <v>45918</v>
       </c>
     </row>
@@ -11737,10 +11725,10 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S166" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S166" s="1" t="n">
         <v>45917</v>
       </c>
     </row>
@@ -11804,10 +11792,10 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S167" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S167" s="1" t="n">
         <v>45915</v>
       </c>
     </row>
@@ -11871,10 +11859,10 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S168" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S168" s="1" t="n">
         <v>45912</v>
       </c>
     </row>
@@ -11938,10 +11926,10 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S169" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S169" s="1" t="n">
         <v>45910</v>
       </c>
     </row>
@@ -12005,10 +11993,10 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S170" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S170" s="1" t="n">
         <v>45904</v>
       </c>
     </row>
@@ -12072,10 +12060,10 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S171" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S171" s="1" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -12139,10 +12127,10 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S172" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S172" s="1" t="n">
         <v>45888</v>
       </c>
     </row>
@@ -12206,10 +12194,10 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S173" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S173" s="1" t="n">
         <v>45884</v>
       </c>
     </row>
@@ -12273,10 +12261,10 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S174" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S174" s="1" t="n">
         <v>45882</v>
       </c>
     </row>
@@ -12340,10 +12328,10 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S175" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S175" s="1" t="n">
         <v>45881</v>
       </c>
     </row>
@@ -12407,10 +12395,10 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S176" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S176" s="1" t="n">
         <v>45878</v>
       </c>
     </row>
@@ -12474,10 +12462,10 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S177" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S177" s="1" t="n">
         <v>45873</v>
       </c>
     </row>
@@ -12541,10 +12529,10 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S178" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S178" s="1" t="n">
         <v>45869</v>
       </c>
     </row>
@@ -12608,10 +12596,10 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S179" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S179" s="1" t="n">
         <v>45860</v>
       </c>
     </row>
@@ -12675,10 +12663,10 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S180" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S180" s="1" t="n">
         <v>45849</v>
       </c>
     </row>
@@ -12742,10 +12730,10 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S181" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S181" s="1" t="n">
         <v>45848</v>
       </c>
     </row>
@@ -12809,10 +12797,10 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S182" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S182" s="1" t="n">
         <v>45848</v>
       </c>
     </row>
@@ -12876,10 +12864,10 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S183" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S183" s="1" t="n">
         <v>45847</v>
       </c>
     </row>
@@ -12943,10 +12931,10 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S184" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S184" s="1" t="n">
         <v>45847</v>
       </c>
     </row>
@@ -13010,10 +12998,10 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S185" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S185" s="1" t="n">
         <v>45841</v>
       </c>
     </row>
@@ -13077,10 +13065,10 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S186" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S186" s="1" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -13144,10 +13132,10 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S187" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S187" s="1" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -13215,10 +13203,10 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S188" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S188" s="1" t="n">
         <v>45834</v>
       </c>
     </row>
@@ -13282,10 +13270,10 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S189" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S189" s="1" t="n">
         <v>45832</v>
       </c>
     </row>
@@ -13349,10 +13337,10 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S190" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S190" s="1" t="n">
         <v>45831</v>
       </c>
     </row>
@@ -13416,10 +13404,10 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S191" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S191" s="1" t="n">
         <v>45825</v>
       </c>
     </row>
@@ -13483,10 +13471,10 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S192" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S192" s="1" t="n">
         <v>45821</v>
       </c>
     </row>
@@ -13550,10 +13538,10 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S193" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S193" s="1" t="n">
         <v>45812</v>
       </c>
     </row>
@@ -13617,10 +13605,10 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S194" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S194" s="1" t="n">
         <v>45800</v>
       </c>
     </row>
@@ -13684,10 +13672,10 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S195" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S195" s="1" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -13751,10 +13739,10 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S196" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S196" s="1" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -13818,10 +13806,10 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S197" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S197" s="1" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -13885,10 +13873,10 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S198" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S198" s="1" t="n">
         <v>45793</v>
       </c>
     </row>
@@ -13952,10 +13940,10 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S199" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S199" s="1" t="n">
         <v>45789</v>
       </c>
     </row>
@@ -14019,10 +14007,10 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S200" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S200" s="1" t="n">
         <v>45771</v>
       </c>
     </row>
@@ -14086,10 +14074,10 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S201" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S201" s="1" t="n">
         <v>45757</v>
       </c>
     </row>
@@ -14153,10 +14141,10 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S202" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S202" s="1" t="n">
         <v>45755</v>
       </c>
     </row>
@@ -14220,10 +14208,10 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S203" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S203" s="1" t="n">
         <v>45750</v>
       </c>
     </row>
@@ -14287,10 +14275,10 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S204" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S204" s="1" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -14354,10 +14342,10 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S205" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S205" s="1" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -14421,10 +14409,10 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S206" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S206" s="1" t="n">
         <v>45743</v>
       </c>
     </row>
@@ -14488,10 +14476,10 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S207" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S207" s="1" t="n">
         <v>45743</v>
       </c>
     </row>
@@ -14555,10 +14543,10 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S208" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S208" s="1" t="n">
         <v>45733</v>
       </c>
     </row>
@@ -14622,10 +14610,10 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S209" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S209" s="1" t="n">
         <v>45733</v>
       </c>
     </row>
@@ -14689,10 +14677,10 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S210" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S210" s="1" t="n">
         <v>45733</v>
       </c>
     </row>
@@ -14756,10 +14744,10 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S211" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S211" s="1" t="n">
         <v>45726</v>
       </c>
     </row>
@@ -14823,10 +14811,10 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S212" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S212" s="1" t="n">
         <v>45721</v>
       </c>
     </row>
@@ -14890,10 +14878,10 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S213" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S213" s="1" t="n">
         <v>45708</v>
       </c>
     </row>
@@ -14957,10 +14945,10 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S214" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S214" s="1" t="n">
         <v>45698</v>
       </c>
     </row>
@@ -15024,10 +15012,10 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S215" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S215" s="1" t="n">
         <v>45691</v>
       </c>
     </row>
@@ -15091,10 +15079,10 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S216" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S216" s="1" t="n">
         <v>45681</v>
       </c>
     </row>
@@ -15158,10 +15146,10 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S217" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S217" s="1" t="n">
         <v>45679</v>
       </c>
     </row>
@@ -15225,10 +15213,10 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S218" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S218" s="1" t="n">
         <v>45674</v>
       </c>
     </row>
@@ -15292,10 +15280,10 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S219" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S219" s="1" t="n">
         <v>45659</v>
       </c>
     </row>
@@ -15359,10 +15347,10 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S220" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S220" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -15426,10 +15414,10 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S221" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S221" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -15493,10 +15481,10 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S222" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S222" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -15560,10 +15548,10 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S223" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S223" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -15627,10 +15615,10 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S224" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S224" s="1" t="n">
         <v>45653</v>
       </c>
     </row>
@@ -15694,10 +15682,10 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S225" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S225" s="1" t="n">
         <v>45653</v>
       </c>
     </row>
@@ -15761,10 +15749,10 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S226" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S226" s="1" t="n">
         <v>45652</v>
       </c>
     </row>
@@ -15828,10 +15816,10 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S227" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S227" s="1" t="n">
         <v>45647</v>
       </c>
     </row>
@@ -15895,10 +15883,10 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S228" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S228" s="1" t="n">
         <v>45642</v>
       </c>
     </row>
@@ -15962,10 +15950,10 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S229" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S229" s="1" t="n">
         <v>45639</v>
       </c>
     </row>
@@ -16029,10 +16017,10 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S230" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S230" s="1" t="n">
         <v>45638</v>
       </c>
     </row>
@@ -16096,10 +16084,10 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S231" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S231" s="1" t="n">
         <v>45626</v>
       </c>
     </row>
@@ -16163,10 +16151,10 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S232" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S232" s="1" t="n">
         <v>45624</v>
       </c>
     </row>
@@ -16230,10 +16218,10 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S233" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S233" s="1" t="n">
         <v>45621</v>
       </c>
     </row>
@@ -16297,10 +16285,10 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S234" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S234" s="1" t="n">
         <v>45621</v>
       </c>
     </row>
@@ -16364,10 +16352,10 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S235" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S235" s="1" t="n">
         <v>45608</v>
       </c>
     </row>
@@ -16431,10 +16419,10 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S236" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S236" s="1" t="n">
         <v>45602</v>
       </c>
     </row>
@@ -16498,10 +16486,10 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S237" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S237" s="1" t="n">
         <v>45588</v>
       </c>
     </row>
@@ -16565,10 +16553,10 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S238" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S238" s="1" t="n">
         <v>45588</v>
       </c>
     </row>
@@ -16632,10 +16620,10 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S239" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S239" s="1" t="n">
         <v>45588</v>
       </c>
     </row>
@@ -16699,10 +16687,10 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S240" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S240" s="1" t="n">
         <v>45562</v>
       </c>
     </row>
@@ -16766,10 +16754,10 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S241" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S241" s="1" t="n">
         <v>45562</v>
       </c>
     </row>
@@ -16833,10 +16821,10 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S242" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S242" s="1" t="n">
         <v>45562</v>
       </c>
     </row>
@@ -16900,10 +16888,10 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S243" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S243" s="1" t="n">
         <v>45558</v>
       </c>
     </row>
@@ -16967,10 +16955,10 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S244" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S244" s="1" t="n">
         <v>45551</v>
       </c>
     </row>
@@ -17034,10 +17022,10 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S245" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S245" s="1" t="n">
         <v>45547</v>
       </c>
     </row>
@@ -17101,10 +17089,10 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S246" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S246" s="1" t="n">
         <v>45545</v>
       </c>
     </row>
@@ -17168,10 +17156,10 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S247" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S247" s="1" t="n">
         <v>45523</v>
       </c>
     </row>
@@ -17235,10 +17223,10 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S248" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S248" s="1" t="n">
         <v>45523</v>
       </c>
     </row>
@@ -17302,10 +17290,10 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S249" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S249" s="1" t="n">
         <v>45517</v>
       </c>
     </row>
@@ -17369,10 +17357,10 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S250" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S250" s="1" t="n">
         <v>45513</v>
       </c>
     </row>
@@ -17436,10 +17424,10 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S251" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S251" s="1" t="n">
         <v>45504</v>
       </c>
     </row>
@@ -17503,10 +17491,10 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S252" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S252" s="1" t="n">
         <v>45504</v>
       </c>
     </row>
@@ -17570,10 +17558,10 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S253" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S253" s="1" t="n">
         <v>45503</v>
       </c>
     </row>
@@ -17637,10 +17625,10 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S254" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S254" s="1" t="n">
         <v>45503</v>
       </c>
     </row>
@@ -17704,10 +17692,10 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S255" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S255" s="1" t="n">
         <v>45495</v>
       </c>
     </row>
@@ -17771,10 +17759,10 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S256" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S256" s="1" t="n">
         <v>45491</v>
       </c>
     </row>
@@ -17838,10 +17826,10 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S257" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S257" s="1" t="n">
         <v>45491</v>
       </c>
     </row>
@@ -17905,10 +17893,10 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S258" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S258" s="1" t="n">
         <v>45489</v>
       </c>
     </row>
@@ -17972,10 +17960,10 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S259" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S259" s="1" t="n">
         <v>45488</v>
       </c>
     </row>
@@ -18039,10 +18027,10 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S260" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S260" s="1" t="n">
         <v>45485</v>
       </c>
     </row>
@@ -18106,10 +18094,10 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S261" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S261" s="1" t="n">
         <v>45482</v>
       </c>
     </row>
@@ -18173,10 +18161,10 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S262" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S262" s="1" t="n">
         <v>45481</v>
       </c>
     </row>
@@ -18240,10 +18228,10 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S263" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S263" s="1" t="n">
         <v>45475</v>
       </c>
     </row>
@@ -18307,10 +18295,10 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S264" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S264" s="1" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -18374,10 +18362,10 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S265" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S265" s="1" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -18441,10 +18429,10 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S266" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S266" s="1" t="n">
         <v>45471</v>
       </c>
     </row>
@@ -18508,10 +18496,10 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S267" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S267" s="1" t="n">
         <v>45469</v>
       </c>
     </row>
@@ -18575,10 +18563,10 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S268" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S268" s="1" t="n">
         <v>45461</v>
       </c>
     </row>
@@ -18642,10 +18630,10 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S269" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S269" s="1" t="n">
         <v>45460</v>
       </c>
     </row>
@@ -18709,10 +18697,10 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S270" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S270" s="1" t="n">
         <v>45460</v>
       </c>
     </row>
@@ -18776,10 +18764,10 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S271" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S271" s="1" t="n">
         <v>45449</v>
       </c>
     </row>
@@ -18843,10 +18831,10 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S272" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S272" s="1" t="n">
         <v>45448</v>
       </c>
     </row>
@@ -18910,10 +18898,10 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S273" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S273" s="1" t="n">
         <v>45443</v>
       </c>
     </row>
@@ -18977,10 +18965,10 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S274" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S274" s="1" t="n">
         <v>45442</v>
       </c>
     </row>
@@ -19044,10 +19032,10 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S275" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S275" s="1" t="n">
         <v>45399</v>
       </c>
     </row>
@@ -19111,10 +19099,10 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S276" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S276" s="1" t="n">
         <v>45394</v>
       </c>
     </row>
@@ -19178,10 +19166,10 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S277" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S277" s="1" t="n">
         <v>45394</v>
       </c>
     </row>
@@ -19245,10 +19233,10 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S278" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S278" s="1" t="n">
         <v>45345</v>
       </c>
     </row>
@@ -19312,10 +19300,10 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S279" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S279" s="1" t="n">
         <v>45345</v>
       </c>
     </row>
@@ -19379,10 +19367,10 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S280" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S280" s="1" t="n">
         <v>45314</v>
       </c>
     </row>
@@ -19446,10 +19434,10 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S281" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S281" s="1" t="n">
         <v>45303</v>
       </c>
     </row>
@@ -19513,10 +19501,10 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S282" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S282" s="1" t="n">
         <v>45300</v>
       </c>
     </row>
@@ -19580,10 +19568,10 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S283" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S283" s="1" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -19647,10 +19635,10 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S284" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S284" s="1" t="n">
         <v>45290</v>
       </c>
     </row>
@@ -19714,10 +19702,10 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S285" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S285" s="1" t="n">
         <v>45285</v>
       </c>
     </row>
@@ -19781,10 +19769,10 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S286" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S286" s="1" t="n">
         <v>45285</v>
       </c>
     </row>
@@ -19848,10 +19836,10 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S287" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S287" s="1" t="n">
         <v>45281</v>
       </c>
     </row>
@@ -19915,10 +19903,10 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S288" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S288" s="1" t="n">
         <v>45275</v>
       </c>
     </row>
@@ -19982,10 +19970,10 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S289" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S289" s="1" t="n">
         <v>45272</v>
       </c>
     </row>
@@ -20049,10 +20037,10 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S290" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S290" s="1" t="n">
         <v>45247</v>
       </c>
     </row>
@@ -20116,10 +20104,10 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S291" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S291" s="1" t="n">
         <v>45245</v>
       </c>
     </row>
@@ -20183,10 +20171,10 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S292" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S292" s="1" t="n">
         <v>45232</v>
       </c>
     </row>
@@ -20250,10 +20238,10 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S293" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S293" s="1" t="n">
         <v>45230</v>
       </c>
     </row>
@@ -20317,10 +20305,10 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S294" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S294" s="1" t="n">
         <v>45201</v>
       </c>
     </row>
@@ -20384,10 +20372,10 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S295" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S295" s="1" t="n">
         <v>45184</v>
       </c>
     </row>
@@ -20451,10 +20439,10 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S296" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S296" s="1" t="n">
         <v>45117</v>
       </c>
     </row>
@@ -20518,10 +20506,10 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S297" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S297" s="1" t="n">
         <v>45105</v>
       </c>
     </row>
@@ -20585,10 +20573,10 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S298" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S298" s="1" t="n">
         <v>45089</v>
       </c>
     </row>
@@ -20652,10 +20640,10 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S299" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S299" s="1" t="n">
         <v>45085</v>
       </c>
     </row>
@@ -20719,10 +20707,10 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S300" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S300" s="1" t="n">
         <v>45072</v>
       </c>
     </row>
@@ -20786,10 +20774,10 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S301" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S301" s="1" t="n">
         <v>45012</v>
       </c>
     </row>
@@ -20853,10 +20841,10 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S302" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S302" s="1" t="n">
         <v>44999</v>
       </c>
     </row>
@@ -20920,10 +20908,10 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S303" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S303" s="1" t="n">
         <v>44999</v>
       </c>
     </row>
@@ -20987,10 +20975,10 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S304" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S304" s="1" t="n">
         <v>44999</v>
       </c>
     </row>
@@ -21054,10 +21042,10 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S305" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S305" s="1" t="n">
         <v>44938</v>
       </c>
     </row>
@@ -21121,10 +21109,10 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S306" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S306" s="1" t="n">
         <v>44925</v>
       </c>
     </row>
@@ -21188,10 +21176,10 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S307" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S307" s="1" t="n">
         <v>44908</v>
       </c>
     </row>
@@ -21255,10 +21243,10 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S308" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S308" s="1" t="n">
         <v>44881</v>
       </c>
     </row>
@@ -21322,10 +21310,10 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S309" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S309" s="1" t="n">
         <v>44839</v>
       </c>
     </row>
@@ -21389,10 +21377,10 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S310" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S310" s="1" t="n">
         <v>44817</v>
       </c>
     </row>
@@ -21456,10 +21444,10 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S311" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S311" s="1" t="n">
         <v>44810</v>
       </c>
     </row>
@@ -21523,10 +21511,10 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S312" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S312" s="1" t="n">
         <v>44810</v>
       </c>
     </row>
@@ -21590,10 +21578,10 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S313" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S313" s="1" t="n">
         <v>44810</v>
       </c>
     </row>
@@ -21657,10 +21645,10 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S314" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S314" s="1" t="n">
         <v>44719</v>
       </c>
     </row>
@@ -21724,10 +21712,10 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S315" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S315" s="1" t="n">
         <v>44691</v>
       </c>
     </row>
@@ -21791,10 +21779,10 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S316" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S316" s="1" t="n">
         <v>44404</v>
       </c>
     </row>
@@ -21858,10 +21846,10 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S317" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S317" s="1" t="n">
         <v>44355</v>
       </c>
     </row>
@@ -21925,10 +21913,10 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S318" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S318" s="1" t="n">
         <v>44118</v>
       </c>
     </row>
@@ -21992,10 +21980,10 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S319" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S319" s="1" t="n">
         <v>43985</v>
       </c>
     </row>
@@ -22059,10 +22047,10 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S320" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S320" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
@@ -22126,10 +22114,10 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S321" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S321" s="1" t="n">
         <v>43720</v>
       </c>
     </row>
@@ -22193,10 +22181,10 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S322" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S322" s="1" t="n">
         <v>43642</v>
       </c>
     </row>
@@ -22260,10 +22248,10 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
-        </is>
-      </c>
-      <c r="S323" s="2" t="n">
+          <t>2026-09-18 07:51:17</t>
+        </is>
+      </c>
+      <c r="S323" s="1" t="n">
         <v>43544</v>
       </c>
     </row>
@@ -22311,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
+          <t>2026-09-18 07:51:17</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22360,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
+          <t>2026-09-18 07:51:17</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22409,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
+          <t>2026-09-18 07:51:17</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22458,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:03</t>
+          <t>2026-09-18 07:51:17</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:17</t>
+          <t>2026-09-18 08:13:32</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:32</t>
+          <t>2026-09-18 08:21:21</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:21</t>
+          <t>2026-09-18 08:49:55</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:55</t>
+          <t>2026-09-18 09:05:35</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:35</t>
+          <t>2026-09-18 09:22:44</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S325" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:44</t>
+          <t>2026-09-18 13:06:54</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>
